--- a/vault/10-domains/shipments/data/attributes-progression-grouping.xlsx
+++ b/vault/10-domains/shipments/data/attributes-progression-grouping.xlsx
@@ -682,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -780,17 +780,17 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Buy Shipment #</t>
+          <t>Odyssey Shipment Identifier</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>11852604</t>
+          <t>C50000003</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A single ID common to the shipment's buy and sell side — what Odyssey sends the customer and the carrier.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Buy Shipment #</t>
+          <t>Odyssey Shipment Identifier</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -813,17 +813,21 @@
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>First character is a letter: O for a single-order shipment, C for a multi-order (consolidated) one.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Sell Shipment #</t>
+          <t>Buy Shipment #</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>25969909</t>
+          <t>11852604</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -838,7 +842,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Sell Shipment #</t>
+          <t>Buy Shipment #</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -856,17 +860,17 @@
     <row r="4">
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Order #</t>
+          <t>Sell Shipment #</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>0000000091000</t>
+          <t>25969909</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Transportation Order #</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -876,7 +880,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Order #</t>
+          <t>Sell Shipment #</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -889,26 +893,22 @@
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>LINX-9742: auto-generated order numbers are digits, customer-provided ones keep letters — hence match: both.</t>
-        </is>
-      </c>
+      <c r="K4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Order Count</t>
+          <t>Order #</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0000000091000</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Count of orders mapped to the shipment.</t>
+          <t>Transportation Order #</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Order Count</t>
+          <t>Order #</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -933,24 +933,24 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>New — not in the stakeholder proposal. exact: true: "Order Count: 2" must not match a count of 12.</t>
+          <t>LINX-9742: auto-generated order numbers are digits, customer-provided ones keep letters — hence match: both.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Pro#/Booking #</t>
+          <t>Order Count</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>441275</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Count of orders mapped to the shipment.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Pro#/Booking #</t>
+          <t>Order Count</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -973,128 +973,132 @@
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>New — not in the stakeholder proposal. exact: true: "Order Count: 2" must not match a count of 12.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>Pro#/Booking #</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>441275</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Text Input</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Pro#/Booking #</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Shipment Identifiers</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Live in search</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>Pickup #</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>PU-929686</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>An ORDER-header reference copied to the load, so a shipment carries N of them.</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Text Input</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Pickup #</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Shipment Identifiers</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>NOW IMPLEMENTED — the stakeholder sheet listed this as "Pickup # (skipped)", marking it missing because it liv…</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Who it belongs to
 ↓</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Customer &amp; Parties involved</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Customers &amp; Parties</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Customer ID</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>WEYERH_01</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Cross customer IDs separated by comma</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Autocomplete Text</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Customer ID</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Customers &amp; Parties</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>Live in search</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Customer Name</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Weyerhaeuser Company</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Autocomplete Text</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>Customer Name</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -1112,17 +1116,17 @@
     <row r="10">
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Consignor</t>
+          <t>Customer Name</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>G2O TECH SOLUTIONS</t>
+          <t>Weyerhaeuser Company</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Name of consignor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -1132,7 +1136,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>Consignor</t>
+          <t>Customer Name</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -1150,119 +1154,119 @@
     <row r="11">
       <c r="D11" s="9" t="inlineStr">
         <is>
+          <t>Consignor</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>G2O TECH SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Name of consignor</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Autocomplete Text</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Consignor</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Customers &amp; Parties</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Live in search</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="D12" s="9" t="inlineStr">
+        <is>
           <t>Consignee</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>SOLVAY CHEMICALS PL</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Name of consignee</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Autocomplete Text</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>Consignee</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Customers &amp; Parties</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="K12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Where it goes
 ↓</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Location &amp; Route</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Route &amp; Geography</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Bastrop LA US 71202</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>First pickup location</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>Autocomplete Text</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>Origin</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>Route &amp; Geography</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>Live in search</t>
-        </is>
-      </c>
-      <c r="K12" s="15" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>Destination</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Green River WY US 82935</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>Last drop off location</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Autocomplete Text</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>Destination</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
@@ -1280,51 +1284,51 @@
     <row r="14">
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr"/>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Green River WY US 82935</t>
+        </is>
+      </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>Miles code</t>
+          <t>Last drop off location</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Numeric Range</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>Not a filter — search bar only</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Autocomplete Text</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Route &amp; Geography</t>
         </is>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>Not in search</t>
-        </is>
-      </c>
-      <c r="K14" s="15" t="inlineStr">
-        <is>
-          <t>Proposed route/geography extra; not shipped — the app implements Origin/Destination only.</t>
-        </is>
-      </c>
+          <t>Live in search</t>
+        </is>
+      </c>
+      <c r="K14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Stops</t>
+          <t>Distance</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr"/>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Count of stops</t>
+          <t>Miles code</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1349,196 +1353,196 @@
       </c>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>Proposed route/geography extra; not shipped.</t>
+          <t>Proposed route/geography extra; not shipped — the app implements Origin/Destination only.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Ship Direction</t>
+          <t>Stops</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr"/>
       <c r="F16" s="15" t="inlineStr">
         <is>
+          <t>Count of stops</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Numeric Range</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>Not a filter — search bar only</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>Not in search</t>
+        </is>
+      </c>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>Proposed route/geography extra; not shipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Ship Direction</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
           <t>Direction of shipment</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>Not a filter — search bar only</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>Not in search</t>
         </is>
       </c>
-      <c r="K16" s="15" t="inlineStr">
+      <c r="K17" s="15" t="inlineStr">
         <is>
           <t>Proposed route/geography extra; not shipped.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>When it moves
 ↓</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Dates &amp; Appointment Windows</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Schedule &amp; Appointments</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>Pickup Date</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>06/05/2026 12:30 CDT</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>Planned Pickup Date</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>Date Picker + Range</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>Pickup Date</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>Schedule &amp; Appointments</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K17" s="21" t="inlineStr">
+      <c r="K18" s="21" t="inlineStr">
         <is>
           <t>Also renders a second field labelled "Pickup Date Range".</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>Delivery Date</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>06/07/2026 12:30 CDT</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>Planned Delivery Date</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>Date Picker + Range</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>Delivery Date</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>Schedule &amp; Appointments</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="inlineStr">
-        <is>
-          <t>Live in search</t>
-        </is>
-      </c>
-      <c r="K18" s="21" t="inlineStr">
-        <is>
-          <t>Also renders a second field labelled "Delivery Date Range".</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>Earliest Pickup Date</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr"/>
+          <t>Delivery Date</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>06/07/2026 12:30 CDT</t>
+        </is>
+      </c>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t>Latest value from orders at first pickup</t>
+          <t>Planned Delivery Date</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>Date Range Picker</t>
-        </is>
-      </c>
-      <c r="H19" s="23" t="inlineStr">
-        <is>
-          <t>Not a filter — search bar only</t>
-        </is>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Date Picker + Range</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>Delivery Date</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>Schedule &amp; Appointments</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
         <is>
-          <t>Not in search</t>
+          <t>Live in search</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
-          <t>The app ships Pickup Date / Delivery Date only; the four order-derived min/max variants were not built.</t>
+          <t>Also renders a second field labelled "Delivery Date Range".</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Latest Pickup Date</t>
+          <t>Earliest Pickup Date</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr"/>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t>Earliest value from orders at first pickup</t>
+          <t>Latest value from orders at first pickup</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -1570,13 +1574,13 @@
     <row r="21">
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>Earliest Delivery Date</t>
+          <t>Latest Pickup Date</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr"/>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>Latest value from orders at last drop off</t>
+          <t>Earliest value from orders at first pickup</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -1608,150 +1612,146 @@
     <row r="22">
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Latest Delivery Date</t>
+          <t>Earliest Delivery Date</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr"/>
       <c r="F22" s="21" t="inlineStr">
         <is>
+          <t>Latest value from orders at last drop off</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>Date Range Picker</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>Not a filter — search bar only</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>Not in search</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>The app ships Pickup Date / Delivery Date only; the four order-derived min/max variants were not built.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>Latest Delivery Date</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr"/>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
           <t>Earliest value from orders at last drop off</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>Date Range Picker</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>Not a filter — search bar only</t>
         </is>
       </c>
-      <c r="I22" s="23" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J22" s="22" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>Not in search</t>
         </is>
       </c>
-      <c r="K22" s="21" t="inlineStr">
+      <c r="K23" s="21" t="inlineStr">
         <is>
           <t>The app ships Pickup Date / Delivery Date only; the four order-derived min/max variants were not built.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>How it moves
 ↓</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Transportation Details</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr">
+      <c r="C24" s="25" t="inlineStr">
         <is>
           <t>Transport &amp; Equipment</t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D24" s="26" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>LTL</t>
         </is>
       </c>
-      <c r="F23" s="27" t="inlineStr">
+      <c r="F24" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G23" s="26" t="inlineStr">
+      <c r="G24" s="26" t="inlineStr">
         <is>
           <t>Dropdown (multi-select)</t>
         </is>
       </c>
-      <c r="H23" s="26" t="inlineStr">
+      <c r="H24" s="26" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="I23" s="26" t="inlineStr">
+      <c r="I24" s="26" t="inlineStr">
         <is>
           <t>Transport &amp; Equipment</t>
         </is>
       </c>
-      <c r="J23" s="28" t="inlineStr">
+      <c r="J24" s="28" t="inlineStr">
         <is>
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K23" s="27" t="inlineStr">
+      <c r="K24" s="27" t="inlineStr">
         <is>
           <t>Exact match only (S130): a substring match over a fixed enum catalog is never what the user meant — "Mode: TL"…</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="D24" s="26" t="inlineStr">
-        <is>
-          <t>Equipment Code</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="inlineStr">
-        <is>
-          <t>LTH</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="26" t="inlineStr">
-        <is>
-          <t>Dropdown (multi-select)</t>
-        </is>
-      </c>
-      <c r="H24" s="26" t="inlineStr">
-        <is>
-          <t>Equipment Code</t>
-        </is>
-      </c>
-      <c r="I24" s="26" t="inlineStr">
-        <is>
-          <t>Transport &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="J24" s="28" t="inlineStr">
-        <is>
-          <t>Live in search</t>
-        </is>
-      </c>
-      <c r="K24" s="27" t="inlineStr">
-        <is>
-          <t>Exact match only (S130), same reasoning as Mode.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="D25" s="26" t="inlineStr">
         <is>
-          <t>Equipment #</t>
+          <t>Equipment Code</t>
         </is>
       </c>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="F25" s="27" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="G25" s="26" t="inlineStr">
         <is>
-          <t>Text Input</t>
+          <t>Dropdown (multi-select)</t>
         </is>
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>Equipment #</t>
+          <t>Equipment Code</t>
         </is>
       </c>
       <c r="I25" s="26" t="inlineStr">
@@ -1779,17 +1779,21 @@
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K25" s="27" t="inlineStr"/>
+      <c r="K25" s="27" t="inlineStr">
+        <is>
+          <t>Exact match only (S130), same reasoning as Mode.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="D26" s="26" t="inlineStr">
         <is>
-          <t>Seal Number</t>
+          <t>Equipment #</t>
         </is>
       </c>
       <c r="E26" s="26" t="inlineStr">
         <is>
-          <t>S447972</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="F26" s="27" t="inlineStr">
@@ -1799,12 +1803,12 @@
       </c>
       <c r="G26" s="26" t="inlineStr">
         <is>
-          <t>Autocomplete Text</t>
+          <t>Text Input</t>
         </is>
       </c>
       <c r="H26" s="26" t="inlineStr">
         <is>
-          <t>Seal Number</t>
+          <t>Equipment #</t>
         </is>
       </c>
       <c r="I26" s="26" t="inlineStr">
@@ -1822,10 +1826,14 @@
     <row r="27">
       <c r="D27" s="26" t="inlineStr">
         <is>
-          <t>Incoterm Info</t>
-        </is>
-      </c>
-      <c r="E27" s="26" t="inlineStr"/>
+          <t>Seal Number</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>S447972</t>
+        </is>
+      </c>
       <c r="F27" s="27" t="inlineStr">
         <is>
           <t>-</t>
@@ -1833,34 +1841,30 @@
       </c>
       <c r="G27" s="26" t="inlineStr">
         <is>
-          <t>Dropdown</t>
-        </is>
-      </c>
-      <c r="H27" s="29" t="inlineStr">
-        <is>
-          <t>Not a filter — search bar only</t>
-        </is>
-      </c>
-      <c r="I27" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Autocomplete Text</t>
+        </is>
+      </c>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>Seal Number</t>
+        </is>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>Transport &amp; Equipment</t>
         </is>
       </c>
       <c r="J27" s="28" t="inlineStr">
         <is>
-          <t>Not in search</t>
-        </is>
-      </c>
-      <c r="K27" s="27" t="inlineStr">
-        <is>
-          <t>Proposed transport/equipment extra; not shipped.</t>
-        </is>
-      </c>
+          <t>Live in search</t>
+        </is>
+      </c>
+      <c r="K27" s="27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="D28" s="26" t="inlineStr">
         <is>
-          <t>Freight Terms</t>
+          <t>Incoterm Info</t>
         </is>
       </c>
       <c r="E28" s="26" t="inlineStr"/>
@@ -1896,119 +1900,115 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Freight Terms</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr"/>
+      <c r="F29" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="H29" s="29" t="inlineStr">
+        <is>
+          <t>Not a filter — search bar only</t>
+        </is>
+      </c>
+      <c r="I29" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="28" t="inlineStr">
+        <is>
+          <t>Not in search</t>
+        </is>
+      </c>
+      <c r="K29" s="27" t="inlineStr">
+        <is>
+          <t>Proposed transport/equipment extra; not shipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>Operational status
 ↓</t>
         </is>
       </c>
-      <c r="B29" s="31" t="inlineStr">
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>Carrier / Tender</t>
         </is>
       </c>
-      <c r="C29" s="31" t="inlineStr">
+      <c r="C30" s="31" t="inlineStr">
         <is>
           <t>Carrier &amp; Tender Status</t>
         </is>
       </c>
-      <c r="D29" s="32" t="inlineStr">
+      <c r="D30" s="32" t="inlineStr">
         <is>
           <t>SCAC</t>
         </is>
       </c>
-      <c r="E29" s="32" t="inlineStr">
+      <c r="E30" s="32" t="inlineStr">
         <is>
           <t>XPOL</t>
         </is>
       </c>
-      <c r="F29" s="33" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>Split from combined SCAC - Tender Status in stakeholder proposal</t>
         </is>
       </c>
-      <c r="G29" s="32" t="inlineStr">
+      <c r="G30" s="32" t="inlineStr">
         <is>
           <t>Autocomplete Text</t>
         </is>
       </c>
-      <c r="H29" s="32" t="inlineStr">
+      <c r="H30" s="32" t="inlineStr">
         <is>
           <t>SCAC</t>
         </is>
       </c>
-      <c r="I29" s="32" t="inlineStr">
+      <c r="I30" s="32" t="inlineStr">
         <is>
           <t>Carrier &amp; Tender Status</t>
         </is>
       </c>
-      <c r="J29" s="34" t="inlineStr">
+      <c r="J30" s="34" t="inlineStr">
         <is>
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K29" s="33" t="inlineStr">
+      <c r="K30" s="33" t="inlineStr">
         <is>
           <t>Added because the stakeholder split the original combined field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="D30" s="32" t="inlineStr">
-        <is>
-          <t>Tender Status</t>
-        </is>
-      </c>
-      <c r="E30" s="32" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="F30" s="33" t="inlineStr">
-        <is>
-          <t>Split from combined SCAC - Tender Status in stakeholder proposal</t>
-        </is>
-      </c>
-      <c r="G30" s="32" t="inlineStr">
-        <is>
-          <t>Dropdown (multi-select)</t>
-        </is>
-      </c>
-      <c r="H30" s="32" t="inlineStr">
-        <is>
-          <t>Tender Status</t>
-        </is>
-      </c>
-      <c r="I30" s="32" t="inlineStr">
-        <is>
-          <t>Carrier &amp; Tender Status</t>
-        </is>
-      </c>
-      <c r="J30" s="34" t="inlineStr">
-        <is>
-          <t>Live in search</t>
-        </is>
-      </c>
-      <c r="K30" s="33" t="inlineStr">
-        <is>
-          <t>Added because the stakeholder split the original combined field. Exact match only (S130).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="D31" s="32" t="inlineStr">
         <is>
-          <t>Shipment Status</t>
+          <t>Tender Status</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="F31" s="33" t="inlineStr">
         <is>
-          <t>Shipment status values</t>
+          <t>Split from combined SCAC - Tender Status in stakeholder proposal</t>
         </is>
       </c>
       <c r="G31" s="32" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="H31" s="32" t="inlineStr">
         <is>
-          <t>Shipment Status</t>
+          <t>Tender Status</t>
         </is>
       </c>
       <c r="I31" s="32" t="inlineStr">
@@ -2033,240 +2033,244 @@
       </c>
       <c r="K31" s="33" t="inlineStr">
         <is>
-          <t>Exact match only (S130).</t>
+          <t>Added because the stakeholder split the original combined field. Exact match only (S130).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="D32" s="32" t="inlineStr">
         <is>
+          <t>Shipment Status</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F32" s="33" t="inlineStr">
+        <is>
+          <t>Shipment status values</t>
+        </is>
+      </c>
+      <c r="G32" s="32" t="inlineStr">
+        <is>
+          <t>Dropdown (multi-select)</t>
+        </is>
+      </c>
+      <c r="H32" s="32" t="inlineStr">
+        <is>
+          <t>Shipment Status</t>
+        </is>
+      </c>
+      <c r="I32" s="32" t="inlineStr">
+        <is>
+          <t>Carrier &amp; Tender Status</t>
+        </is>
+      </c>
+      <c r="J32" s="34" t="inlineStr">
+        <is>
+          <t>Live in search</t>
+        </is>
+      </c>
+      <c r="K32" s="33" t="inlineStr">
+        <is>
+          <t>Exact match only (S130).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" s="32" t="inlineStr">
+        <is>
           <t>SCAC - Tender Status (combined)</t>
         </is>
       </c>
-      <c r="E32" s="32" t="inlineStr"/>
-      <c r="F32" s="33" t="inlineStr"/>
-      <c r="G32" s="32" t="inlineStr">
+      <c r="E33" s="32" t="inlineStr"/>
+      <c r="F33" s="33" t="inlineStr"/>
+      <c r="G33" s="32" t="inlineStr">
         <is>
           <t>Proposed — no control built</t>
         </is>
       </c>
-      <c r="H32" s="35" t="inlineStr">
+      <c r="H33" s="35" t="inlineStr">
         <is>
           <t>Not a filter — search bar only</t>
         </is>
       </c>
-      <c r="I32" s="35" t="inlineStr">
+      <c r="I33" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J32" s="34" t="inlineStr">
+      <c r="J33" s="34" t="inlineStr">
         <is>
           <t>Not in search (skipped in proposal)</t>
         </is>
       </c>
-      <c r="K32" s="33" t="inlineStr">
+      <c r="K33" s="33" t="inlineStr">
         <is>
           <t>Skipped; the stakeholder split produced the two separate SCAC and Tender Status attributes the app implements.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="36" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>Shipment classification
 ↓</t>
         </is>
       </c>
-      <c r="B33" s="37" t="inlineStr">
+      <c r="B34" s="37" t="inlineStr">
         <is>
           <t>Others</t>
         </is>
       </c>
-      <c r="C33" s="37" t="inlineStr">
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>Classification</t>
         </is>
       </c>
-      <c r="D33" s="38" t="inlineStr">
+      <c r="D34" s="38" t="inlineStr">
         <is>
           <t>Shipment Type</t>
         </is>
       </c>
-      <c r="E33" s="38" t="inlineStr">
+      <c r="E34" s="38" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="F33" s="39" t="inlineStr">
+      <c r="F34" s="39" t="inlineStr">
         <is>
           <t>Direct (1 mapped order) vs Consolidation (&gt;1 mapped orders), LINX-11597 verbatim.</t>
         </is>
       </c>
-      <c r="G33" s="38" t="inlineStr">
+      <c r="G34" s="38" t="inlineStr">
         <is>
           <t>Dropdown (multi-select)</t>
         </is>
       </c>
-      <c r="H33" s="38" t="inlineStr">
+      <c r="H34" s="38" t="inlineStr">
         <is>
           <t>Shipment Type</t>
         </is>
       </c>
-      <c r="I33" s="38" t="inlineStr">
+      <c r="I34" s="38" t="inlineStr">
         <is>
           <t>Classification</t>
         </is>
       </c>
-      <c r="J33" s="40" t="inlineStr">
+      <c r="J34" s="40" t="inlineStr">
         <is>
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K33" s="39" t="inlineStr">
+      <c r="K34" s="39" t="inlineStr">
         <is>
           <t>New since S108. Deliberately NOT promoted to the top of the progression: prime empty-input suggestion slots be…</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="D34" s="38" t="inlineStr">
+    <row r="35">
+      <c r="D35" s="38" t="inlineStr">
         <is>
           <t>Planning Type</t>
         </is>
       </c>
-      <c r="E34" s="38" t="inlineStr">
+      <c r="E35" s="38" t="inlineStr">
         <is>
           <t>SSD</t>
         </is>
       </c>
-      <c r="F34" s="39" t="inlineStr">
+      <c r="F35" s="39" t="inlineStr">
         <is>
           <t>RDD if ANY mapped order is RDD, else SSD, LINX-12902 verbatim.</t>
         </is>
       </c>
-      <c r="G34" s="38" t="inlineStr">
+      <c r="G35" s="38" t="inlineStr">
         <is>
           <t>Dropdown (multi-select)</t>
         </is>
       </c>
-      <c r="H34" s="38" t="inlineStr">
+      <c r="H35" s="38" t="inlineStr">
         <is>
           <t>Planning Type</t>
         </is>
       </c>
-      <c r="I34" s="38" t="inlineStr">
+      <c r="I35" s="38" t="inlineStr">
         <is>
           <t>Classification</t>
         </is>
       </c>
-      <c r="J34" s="40" t="inlineStr">
+      <c r="J35" s="40" t="inlineStr">
         <is>
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K34" s="39" t="inlineStr">
+      <c r="K35" s="39" t="inlineStr">
         <is>
           <t>New since S108, alongside Shipment Type. Deliberately NOT promoted to the top of the progression — same reason…</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="41" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr">
         <is>
           <t>Cargo details
 ↓</t>
         </is>
       </c>
-      <c r="B35" s="42" t="inlineStr">
+      <c r="B36" s="42" t="inlineStr">
         <is>
           <t>Weight, Quantity &amp; Handling</t>
         </is>
       </c>
-      <c r="C35" s="42" t="inlineStr">
+      <c r="C36" s="42" t="inlineStr">
         <is>
           <t>Cargo &amp; Handling</t>
         </is>
       </c>
-      <c r="D35" s="43" t="inlineStr">
+      <c r="D36" s="43" t="inlineStr">
         <is>
           <t>Gross Weight</t>
         </is>
       </c>
-      <c r="E35" s="43" t="inlineStr">
+      <c r="E36" s="43" t="inlineStr">
         <is>
           <t>6129</t>
         </is>
       </c>
-      <c r="F35" s="44" t="inlineStr">
+      <c r="F36" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G35" s="43" t="inlineStr">
+      <c r="G36" s="43" t="inlineStr">
         <is>
           <t>Text Input</t>
         </is>
       </c>
-      <c r="H35" s="43" t="inlineStr">
+      <c r="H36" s="43" t="inlineStr">
         <is>
           <t>Gross Weight</t>
         </is>
       </c>
-      <c r="I35" s="43" t="inlineStr">
+      <c r="I36" s="43" t="inlineStr">
         <is>
           <t>Cargo &amp; Handling</t>
         </is>
       </c>
-      <c r="J35" s="45" t="inlineStr">
+      <c r="J36" s="45" t="inlineStr">
         <is>
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K35" s="44" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="D36" s="43" t="inlineStr">
-        <is>
-          <t>Net Weight</t>
-        </is>
-      </c>
-      <c r="E36" s="43" t="inlineStr"/>
-      <c r="F36" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="43" t="inlineStr">
-        <is>
-          <t>Numeric Range</t>
-        </is>
-      </c>
-      <c r="H36" s="46" t="inlineStr">
-        <is>
-          <t>Not a filter — search bar only</t>
-        </is>
-      </c>
-      <c r="I36" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" s="45" t="inlineStr">
-        <is>
-          <t>Not in search</t>
-        </is>
-      </c>
-      <c r="K36" s="44" t="inlineStr">
-        <is>
-          <t>The app ships Gross Weight only.</t>
-        </is>
-      </c>
+      <c r="K36" s="44" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="D37" s="43" t="inlineStr">
         <is>
-          <t>Tare Weight</t>
+          <t>Net Weight</t>
         </is>
       </c>
       <c r="E37" s="43" t="inlineStr"/>
@@ -2304,13 +2308,13 @@
     <row r="38">
       <c r="D38" s="43" t="inlineStr">
         <is>
-          <t>Pkg Count</t>
+          <t>Tare Weight</t>
         </is>
       </c>
       <c r="E38" s="43" t="inlineStr"/>
       <c r="F38" s="44" t="inlineStr">
         <is>
-          <t>Total package count</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G38" s="43" t="inlineStr">
@@ -2342,143 +2346,143 @@
     <row r="39">
       <c r="D39" s="43" t="inlineStr">
         <is>
-          <t>Hazardous (Y/N)</t>
+          <t>Pkg Count</t>
         </is>
       </c>
       <c r="E39" s="43" t="inlineStr"/>
       <c r="F39" s="44" t="inlineStr">
         <is>
+          <t>Total package count</t>
+        </is>
+      </c>
+      <c r="G39" s="43" t="inlineStr">
+        <is>
+          <t>Numeric Range</t>
+        </is>
+      </c>
+      <c r="H39" s="46" t="inlineStr">
+        <is>
+          <t>Not a filter — search bar only</t>
+        </is>
+      </c>
+      <c r="I39" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="45" t="inlineStr">
+        <is>
+          <t>Not in search</t>
+        </is>
+      </c>
+      <c r="K39" s="44" t="inlineStr">
+        <is>
+          <t>The app ships Gross Weight only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="D40" s="43" t="inlineStr">
+        <is>
+          <t>Hazardous (Y/N)</t>
+        </is>
+      </c>
+      <c r="E40" s="43" t="inlineStr"/>
+      <c r="F40" s="44" t="inlineStr">
+        <is>
           <t>Hazardous indicator</t>
         </is>
       </c>
-      <c r="G39" s="43" t="inlineStr">
+      <c r="G40" s="43" t="inlineStr">
         <is>
           <t>Toggle</t>
         </is>
       </c>
-      <c r="H39" s="46" t="inlineStr">
+      <c r="H40" s="46" t="inlineStr">
         <is>
           <t>Not a filter — search bar only</t>
         </is>
       </c>
-      <c r="I39" s="46" t="inlineStr">
+      <c r="I40" s="46" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J39" s="45" t="inlineStr">
+      <c r="J40" s="45" t="inlineStr">
         <is>
           <t>Not in search</t>
         </is>
       </c>
-      <c r="K39" s="44" t="inlineStr">
+      <c r="K40" s="44" t="inlineStr">
         <is>
           <t>The app ships Gross Weight only.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="47" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="47" t="inlineStr">
         <is>
           <t>Financial details
 ↓</t>
         </is>
       </c>
-      <c r="B40" s="48" t="inlineStr">
+      <c r="B41" s="48" t="inlineStr">
         <is>
           <t>Rate details</t>
         </is>
       </c>
-      <c r="C40" s="48" t="inlineStr">
+      <c r="C41" s="48" t="inlineStr">
         <is>
           <t>Rates &amp; Costs</t>
         </is>
       </c>
-      <c r="D40" s="49" t="inlineStr">
+      <c r="D41" s="49" t="inlineStr">
         <is>
           <t>AP Freight Cost</t>
         </is>
       </c>
-      <c r="E40" s="49" t="inlineStr">
+      <c r="E41" s="49" t="inlineStr">
         <is>
           <t>4,624.99</t>
         </is>
       </c>
-      <c r="F40" s="50" t="inlineStr">
+      <c r="F41" s="50" t="inlineStr">
         <is>
           <t>Total AP freight cost</t>
         </is>
       </c>
-      <c r="G40" s="49" t="inlineStr">
+      <c r="G41" s="49" t="inlineStr">
         <is>
           <t>Text Input</t>
         </is>
       </c>
-      <c r="H40" s="49" t="inlineStr">
+      <c r="H41" s="49" t="inlineStr">
         <is>
           <t>AP Freight Cost</t>
         </is>
       </c>
-      <c r="I40" s="49" t="inlineStr">
+      <c r="I41" s="49" t="inlineStr">
         <is>
           <t>Rates &amp; Costs</t>
         </is>
       </c>
-      <c r="J40" s="51" t="inlineStr">
+      <c r="J41" s="51" t="inlineStr">
         <is>
           <t>Live in search</t>
         </is>
       </c>
-      <c r="K40" s="50" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="D41" s="49" t="inlineStr">
-        <is>
-          <t>Preferred AP Direct Cost</t>
-        </is>
-      </c>
-      <c r="E41" s="49" t="inlineStr"/>
-      <c r="F41" s="50" t="inlineStr">
-        <is>
-          <t>Direct AP cost</t>
-        </is>
-      </c>
-      <c r="G41" s="49" t="inlineStr">
-        <is>
-          <t>Numeric Range</t>
-        </is>
-      </c>
-      <c r="H41" s="52" t="inlineStr">
-        <is>
-          <t>Not a filter — search bar only</t>
-        </is>
-      </c>
-      <c r="I41" s="52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J41" s="51" t="inlineStr">
-        <is>
-          <t>Not in search</t>
-        </is>
-      </c>
-      <c r="K41" s="50" t="inlineStr">
-        <is>
-          <t>The app ships AP Freight Cost only.</t>
-        </is>
-      </c>
+      <c r="K41" s="50" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="D42" s="49" t="inlineStr">
         <is>
-          <t>AR Freight Cost</t>
+          <t>Preferred AP Direct Cost</t>
         </is>
       </c>
       <c r="E42" s="49" t="inlineStr"/>
       <c r="F42" s="50" t="inlineStr">
         <is>
-          <t>Total AR freight cost</t>
+          <t>Direct AP cost</t>
         </is>
       </c>
       <c r="G42" s="49" t="inlineStr">
@@ -2510,119 +2514,119 @@
     <row r="43">
       <c r="D43" s="49" t="inlineStr">
         <is>
-          <t>Preferred AR Direct Cost</t>
+          <t>AR Freight Cost</t>
         </is>
       </c>
       <c r="E43" s="49" t="inlineStr"/>
       <c r="F43" s="50" t="inlineStr">
         <is>
+          <t>Total AR freight cost</t>
+        </is>
+      </c>
+      <c r="G43" s="49" t="inlineStr">
+        <is>
+          <t>Numeric Range</t>
+        </is>
+      </c>
+      <c r="H43" s="52" t="inlineStr">
+        <is>
+          <t>Not a filter — search bar only</t>
+        </is>
+      </c>
+      <c r="I43" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="51" t="inlineStr">
+        <is>
+          <t>Not in search</t>
+        </is>
+      </c>
+      <c r="K43" s="50" t="inlineStr">
+        <is>
+          <t>The app ships AP Freight Cost only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" s="49" t="inlineStr">
+        <is>
+          <t>Preferred AR Direct Cost</t>
+        </is>
+      </c>
+      <c r="E44" s="49" t="inlineStr"/>
+      <c r="F44" s="50" t="inlineStr">
+        <is>
           <t>Direct AR cost</t>
         </is>
       </c>
-      <c r="G43" s="49" t="inlineStr">
+      <c r="G44" s="49" t="inlineStr">
         <is>
           <t>Numeric Range</t>
         </is>
       </c>
-      <c r="H43" s="52" t="inlineStr">
+      <c r="H44" s="52" t="inlineStr">
         <is>
           <t>Not a filter — search bar only</t>
         </is>
       </c>
-      <c r="I43" s="52" t="inlineStr">
+      <c r="I44" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J43" s="51" t="inlineStr">
+      <c r="J44" s="51" t="inlineStr">
         <is>
           <t>Not in search</t>
         </is>
       </c>
-      <c r="K43" s="50" t="inlineStr">
+      <c r="K44" s="50" t="inlineStr">
         <is>
           <t>The app ships AP Freight Cost only.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="53" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="53" t="inlineStr">
         <is>
           <t>Load logistics
 ↓</t>
         </is>
       </c>
-      <c r="B44" s="54" t="inlineStr">
+      <c r="B45" s="54" t="inlineStr">
         <is>
           <t>Load information</t>
         </is>
       </c>
-      <c r="C44" s="54" t="inlineStr">
+      <c r="C45" s="54" t="inlineStr">
         <is>
           <t>Load Details</t>
         </is>
       </c>
-      <c r="D44" s="55" t="inlineStr">
+      <c r="D45" s="55" t="inlineStr">
         <is>
           <t>Load #</t>
         </is>
       </c>
-      <c r="E44" s="55" t="inlineStr">
+      <c r="E45" s="55" t="inlineStr">
         <is>
           <t>23492</t>
         </is>
       </c>
-      <c r="F44" s="56" t="inlineStr">
+      <c r="F45" s="56" t="inlineStr">
         <is>
           <t>Load numbers in shipment</t>
         </is>
       </c>
-      <c r="G44" s="55" t="inlineStr">
+      <c r="G45" s="55" t="inlineStr">
         <is>
           <t>Text Input</t>
         </is>
       </c>
-      <c r="H44" s="55" t="inlineStr">
+      <c r="H45" s="55" t="inlineStr">
         <is>
           <t>Load #</t>
-        </is>
-      </c>
-      <c r="I44" s="55" t="inlineStr">
-        <is>
-          <t>Load Details</t>
-        </is>
-      </c>
-      <c r="J44" s="57" t="inlineStr">
-        <is>
-          <t>Live in search</t>
-        </is>
-      </c>
-      <c r="K44" s="56" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="D45" s="55" t="inlineStr">
-        <is>
-          <t>Load Count</t>
-        </is>
-      </c>
-      <c r="E45" s="55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F45" s="56" t="inlineStr">
-        <is>
-          <t>Count of loads in shipment</t>
-        </is>
-      </c>
-      <c r="G45" s="55" t="inlineStr">
-        <is>
-          <t>Text Input</t>
-        </is>
-      </c>
-      <c r="H45" s="55" t="inlineStr">
-        <is>
-          <t>Load Count</t>
         </is>
       </c>
       <c r="I45" s="55" t="inlineStr">
@@ -2640,139 +2644,139 @@
     <row r="46">
       <c r="D46" s="55" t="inlineStr">
         <is>
+          <t>Load Count</t>
+        </is>
+      </c>
+      <c r="E46" s="55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F46" s="56" t="inlineStr">
+        <is>
+          <t>Count of loads in shipment</t>
+        </is>
+      </c>
+      <c r="G46" s="55" t="inlineStr">
+        <is>
+          <t>Text Input</t>
+        </is>
+      </c>
+      <c r="H46" s="55" t="inlineStr">
+        <is>
+          <t>Load Count</t>
+        </is>
+      </c>
+      <c r="I46" s="55" t="inlineStr">
+        <is>
+          <t>Load Details</t>
+        </is>
+      </c>
+      <c r="J46" s="57" t="inlineStr">
+        <is>
+          <t>Live in search</t>
+        </is>
+      </c>
+      <c r="K46" s="56" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="D47" s="55" t="inlineStr">
+        <is>
           <t>Load Status</t>
         </is>
       </c>
-      <c r="E46" s="55" t="inlineStr"/>
-      <c r="F46" s="56" t="inlineStr">
+      <c r="E47" s="55" t="inlineStr"/>
+      <c r="F47" s="56" t="inlineStr">
         <is>
           <t>Load operational status</t>
         </is>
       </c>
-      <c r="G46" s="55" t="inlineStr">
+      <c r="G47" s="55" t="inlineStr">
         <is>
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="H46" s="58" t="inlineStr">
+      <c r="H47" s="58" t="inlineStr">
         <is>
           <t>Not a filter — search bar only</t>
         </is>
       </c>
-      <c r="I46" s="58" t="inlineStr">
+      <c r="I47" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J46" s="57" t="inlineStr">
+      <c r="J47" s="57" t="inlineStr">
         <is>
           <t>Not in search</t>
         </is>
       </c>
-      <c r="K46" s="56" t="inlineStr">
+      <c r="K47" s="56" t="inlineStr">
         <is>
           <t>Proposed load-details extra; not shipped.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="59" t="inlineStr"/>
-      <c r="B47" s="60" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="59" t="inlineStr"/>
+      <c r="B48" s="60" t="inlineStr">
         <is>
           <t>n/a — grid-column derived</t>
         </is>
       </c>
-      <c r="C47" s="60" t="inlineStr">
+      <c r="C48" s="60" t="inlineStr">
         <is>
           <t>Advanced / Rare Fields</t>
         </is>
       </c>
-      <c r="D47" s="61" t="inlineStr">
+      <c r="D48" s="61" t="inlineStr">
         <is>
           <t>Shipment Type (Pooling · Cross customer · Line haul · Rule 11)</t>
         </is>
       </c>
-      <c r="E47" s="61" t="inlineStr"/>
-      <c r="F47" s="62" t="inlineStr"/>
-      <c r="G47" s="61" t="inlineStr">
+      <c r="E48" s="61" t="inlineStr"/>
+      <c r="F48" s="62" t="inlineStr"/>
+      <c r="G48" s="61" t="inlineStr">
         <is>
           <t>Proposed — no control built</t>
         </is>
       </c>
-      <c r="H47" s="63" t="inlineStr">
+      <c r="H48" s="63" t="inlineStr">
         <is>
           <t>Not a filter — search bar only</t>
         </is>
       </c>
-      <c r="I47" s="63" t="inlineStr">
+      <c r="I48" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J47" s="64" t="inlineStr">
+      <c r="J48" s="64" t="inlineStr">
         <is>
           <t>Not in search</t>
         </is>
       </c>
-      <c r="K47" s="62" t="inlineStr">
+      <c r="K48" s="62" t="inlineStr">
         <is>
           <t>NAME COLLISION: the implemented "Shipment Type" (Direct/Consolidation, LINX-11597) is a DIFFERENT attribute wi…</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="D48" s="61" t="inlineStr">
-        <is>
-          <t>Shipment Sequence Leg</t>
-        </is>
-      </c>
-      <c r="E48" s="61" t="inlineStr"/>
-      <c r="F48" s="62" t="inlineStr">
-        <is>
-          <t>Leg of multi-leg shipment</t>
-        </is>
-      </c>
-      <c r="G48" s="61" t="inlineStr">
-        <is>
-          <t>Dropdown</t>
-        </is>
-      </c>
-      <c r="H48" s="63" t="inlineStr">
-        <is>
-          <t>Not a filter — search bar only</t>
-        </is>
-      </c>
-      <c r="I48" s="63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J48" s="64" t="inlineStr">
-        <is>
-          <t>Not in search</t>
-        </is>
-      </c>
-      <c r="K48" s="62" t="inlineStr">
-        <is>
-          <t>Field `shipmentSequenceLeg` EXISTS on the shipment row; never exposed to search.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="D49" s="61" t="inlineStr">
         <is>
-          <t>Next Shipment ID</t>
+          <t>Shipment Sequence Leg</t>
         </is>
       </c>
       <c r="E49" s="61" t="inlineStr"/>
       <c r="F49" s="62" t="inlineStr">
         <is>
-          <t>Used for pooling or Rule 11</t>
+          <t>Leg of multi-leg shipment</t>
         </is>
       </c>
       <c r="G49" s="61" t="inlineStr">
         <is>
-          <t>Text Input</t>
+          <t>Dropdown</t>
         </is>
       </c>
       <c r="H49" s="63" t="inlineStr">
@@ -2792,43 +2796,81 @@
       </c>
       <c r="K49" s="62" t="inlineStr">
         <is>
-          <t>Field `nextShipmentId` EXISTS on the shipment row; never exposed to search.</t>
+          <t>Field `shipmentSequenceLeg` EXISTS on the shipment row; never exposed to search.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="D50" s="61" t="inlineStr">
         <is>
-          <t>Validation Message</t>
+          <t>Next Shipment ID</t>
         </is>
       </c>
       <c r="E50" s="61" t="inlineStr"/>
       <c r="F50" s="62" t="inlineStr">
         <is>
+          <t>Used for pooling or Rule 11</t>
+        </is>
+      </c>
+      <c r="G50" s="61" t="inlineStr">
+        <is>
+          <t>Text Input</t>
+        </is>
+      </c>
+      <c r="H50" s="63" t="inlineStr">
+        <is>
+          <t>Not a filter — search bar only</t>
+        </is>
+      </c>
+      <c r="I50" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J50" s="64" t="inlineStr">
+        <is>
+          <t>Not in search</t>
+        </is>
+      </c>
+      <c r="K50" s="62" t="inlineStr">
+        <is>
+          <t>Field `nextShipmentId` EXISTS on the shipment row; never exposed to search.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="D51" s="61" t="inlineStr">
+        <is>
+          <t>Validation Message</t>
+        </is>
+      </c>
+      <c r="E51" s="61" t="inlineStr"/>
+      <c r="F51" s="62" t="inlineStr">
+        <is>
           <t>User review validation message missing from stakeholder grouping</t>
         </is>
       </c>
-      <c r="G50" s="61" t="inlineStr">
+      <c r="G51" s="61" t="inlineStr">
         <is>
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="H50" s="63" t="inlineStr">
+      <c r="H51" s="63" t="inlineStr">
         <is>
           <t>Not a filter — search bar only</t>
         </is>
       </c>
-      <c r="I50" s="63" t="inlineStr">
+      <c r="I51" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J50" s="64" t="inlineStr">
+      <c r="J51" s="64" t="inlineStr">
         <is>
           <t>Not in search (skipped in proposal)</t>
         </is>
       </c>
-      <c r="K50" s="62" t="inlineStr">
+      <c r="K51" s="62" t="inlineStr">
         <is>
           <t>Field `validationMessage` EXISTS on the shipment row; never exposed to search.</t>
         </is>
@@ -2836,39 +2878,39 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="B47:B50"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="A35:A39"/>
-    <mergeCell ref="B17:B22"/>
-    <mergeCell ref="C47:C50"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="B35:B39"/>
-    <mergeCell ref="C40:C43"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C2:C7"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="C23:C28"/>
-    <mergeCell ref="C35:C39"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="C17:C22"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="C18:C23"/>
+    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="C24:C29"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="C36:C40"/>
+    <mergeCell ref="C2:C8"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B36:B40"/>
+    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A36:A40"/>
+    <mergeCell ref="B24:B29"/>
+    <mergeCell ref="C48:C51"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="B2:B8"/>
+    <mergeCell ref="B41:B44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/vault/10-domains/shipments/data/attributes-progression-grouping.xlsx
+++ b/vault/10-domains/shipments/data/attributes-progression-grouping.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Odyssey Shipment Identifier</t>
+          <t>Odyssey Shipment ID</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Odyssey Shipment Identifier</t>
+          <t>Odyssey Shipment ID</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">

--- a/vault/10-domains/shipments/data/attributes-progression-grouping.xlsx
+++ b/vault/10-domains/shipments/data/attributes-progression-grouping.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>G2O TECH SOLUTIONS</t>
+          <t>BASTROP TERMINAL</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>SOLVAY CHEMICALS PL</t>
+          <t>GREEN RIVER TERMINAL</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
